--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_6.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4625 +469,6240 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.494</t>
+          <t>2026-05-29 09:35:57.210</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421734918</v>
+        <v>1780022150854</v>
       </c>
       <c r="C2" t="n">
-        <v>89596</v>
+        <v>83179</v>
       </c>
       <c r="D2" t="n">
-        <v>-54.12</v>
+        <v>-1249.8</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G2" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.495</t>
+          <t>2026-05-29 09:35:57.211</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421735119</v>
+        <v>1780022151054</v>
       </c>
       <c r="C3" t="n">
-        <v>89160</v>
+        <v>83205</v>
       </c>
       <c r="D3" t="n">
-        <v>-487.42</v>
+        <v>-1161.31</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G3" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6156</v>
+      </c>
+      <c r="L3" t="n">
+        <v>114</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.496</t>
+          <t>2026-05-29 09:35:57.213</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421735320</v>
+        <v>1780022151254</v>
       </c>
       <c r="C4" t="n">
-        <v>89154</v>
+        <v>82541</v>
       </c>
       <c r="D4" t="n">
-        <v>-469.04</v>
+        <v>-1767.24</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G4" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5958</v>
+      </c>
+      <c r="L4" t="n">
+        <v>106</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.391</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.499</t>
+          <t>2026-05-29 09:35:57.214</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421735522</v>
+        <v>1780022151454</v>
       </c>
       <c r="C5" t="n">
-        <v>89375</v>
+        <v>82665</v>
       </c>
       <c r="D5" t="n">
-        <v>-224.59</v>
+        <v>-1554.88</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G5" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5759</v>
+      </c>
+      <c r="L5" t="n">
+        <v>113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.721</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.500</t>
+          <t>2026-05-29 09:35:57.215</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421735723</v>
+        <v>1780022151654</v>
       </c>
       <c r="C6" t="n">
-        <v>89502</v>
+        <v>82443</v>
       </c>
       <c r="D6" t="n">
-        <v>-86.36</v>
+        <v>-1699.14</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>1974</v>
+        <v>7437</v>
       </c>
       <c r="G6" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5560</v>
+      </c>
+      <c r="L6" t="n">
+        <v>108</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.922</t>
+          <t>2026-05-29 09:35:57.485</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421735925</v>
+        <v>1780022151854</v>
       </c>
       <c r="C7" t="n">
-        <v>88996</v>
+        <v>82673</v>
       </c>
       <c r="D7" t="n">
-        <v>-588.04</v>
+        <v>-1384.18</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>1974</v>
+        <v>7437</v>
       </c>
       <c r="G7" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5630</v>
+      </c>
+      <c r="L7" t="n">
+        <v>109</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:53.923</t>
+          <t>2026-05-29 09:35:57.487</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421736126</v>
+        <v>1780022152054</v>
       </c>
       <c r="C8" t="n">
-        <v>89126</v>
+        <v>82223</v>
       </c>
       <c r="D8" t="n">
-        <v>-428.64</v>
+        <v>-1764.97</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>1974</v>
+        <v>7437</v>
       </c>
       <c r="G8" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="L8" t="n">
+        <v>108</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:54.346</t>
+          <t>2026-05-29 09:35:57.488</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421736327</v>
+        <v>1780022152254</v>
       </c>
       <c r="C9" t="n">
-        <v>89271</v>
+        <v>81617</v>
       </c>
       <c r="D9" t="n">
-        <v>-262.21</v>
+        <v>-2282.72</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>1974</v>
+        <v>7437</v>
       </c>
       <c r="G9" t="n">
-        <v>206.32</v>
+        <v>252.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5233</v>
+      </c>
+      <c r="L9" t="n">
+        <v>111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:54.347</t>
+          <t>2026-05-29 09:35:57.489</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421736529</v>
+        <v>1780022152473</v>
       </c>
       <c r="C10" t="n">
-        <v>89358</v>
+        <v>81995</v>
       </c>
       <c r="D10" t="n">
-        <v>-162.1</v>
+        <v>-1790.59</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G10" t="n">
-        <v>205.68</v>
+        <v>252.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5015</v>
+      </c>
+      <c r="L10" t="n">
+        <v>107</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.823</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:54.733</t>
+          <t>2026-05-29 09:35:57.490</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421736730</v>
+        <v>1780022153193</v>
       </c>
       <c r="C11" t="n">
-        <v>88929</v>
+        <v>83128</v>
       </c>
       <c r="D11" t="n">
-        <v>-582.99</v>
+        <v>-568.0599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G11" t="n">
-        <v>205.68</v>
+        <v>252.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4296</v>
+      </c>
+      <c r="L11" t="n">
+        <v>116</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:54.760</t>
+          <t>2026-05-29 09:35:57.491</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421736932</v>
+        <v>1780022153393</v>
       </c>
       <c r="C12" t="n">
-        <v>89141</v>
+        <v>84686</v>
       </c>
       <c r="D12" t="n">
-        <v>-341.84</v>
+        <v>1018.34</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>805</v>
+        <v>21410</v>
       </c>
       <c r="G12" t="n">
-        <v>205.68</v>
+        <v>252.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4097</v>
+      </c>
+      <c r="L12" t="n">
+        <v>119</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.019</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:55.471</t>
+          <t>2026-05-29 09:35:57.493</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421737133</v>
+        <v>1780022153593</v>
       </c>
       <c r="C13" t="n">
-        <v>89297</v>
+        <v>84896</v>
       </c>
       <c r="D13" t="n">
-        <v>-168.75</v>
+        <v>1177.43</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>805</v>
+        <v>21410</v>
       </c>
       <c r="G13" t="n">
-        <v>205.68</v>
+        <v>252.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3898</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:55.471</t>
+          <t>2026-05-29 09:35:57.494</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421737334</v>
+        <v>1780022153793</v>
       </c>
       <c r="C14" t="n">
-        <v>89482</v>
+        <v>84803</v>
       </c>
       <c r="D14" t="n">
-        <v>24.68</v>
+        <v>1025.56</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>705</v>
+        <v>21410</v>
       </c>
       <c r="G14" t="n">
-        <v>124.57</v>
+        <v>252.6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3700</v>
+      </c>
+      <c r="L14" t="n">
+        <v>115</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:55.473</t>
+          <t>2026-05-29 09:35:57.839</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421737536</v>
+        <v>1780022153994</v>
       </c>
       <c r="C15" t="n">
-        <v>89005</v>
+        <v>84948</v>
       </c>
       <c r="D15" t="n">
-        <v>-453.55</v>
+        <v>1119.28</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>705</v>
+        <v>21410</v>
       </c>
       <c r="G15" t="n">
-        <v>124.57</v>
+        <v>252.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3843</v>
+      </c>
+      <c r="L15" t="n">
+        <v>112</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.813</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:55.474</t>
+          <t>2026-05-29 09:35:57.841</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421737737</v>
+        <v>1780022154193</v>
       </c>
       <c r="C16" t="n">
-        <v>89182</v>
+        <v>86330</v>
       </c>
       <c r="D16" t="n">
-        <v>-253.87</v>
+        <v>2445.31</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
-        <v>705</v>
+        <v>21410</v>
       </c>
       <c r="G16" t="n">
-        <v>124.57</v>
+        <v>252.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3646</v>
+      </c>
+      <c r="L16" t="n">
+        <v>118</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.324</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:55.770</t>
+          <t>2026-05-29 09:35:57.843</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421737938</v>
+        <v>1780022154393</v>
       </c>
       <c r="C17" t="n">
-        <v>89270</v>
+        <v>86365</v>
       </c>
       <c r="D17" t="n">
-        <v>-153.18</v>
+        <v>2358.05</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>705</v>
+        <v>21410</v>
       </c>
       <c r="G17" t="n">
-        <v>124.57</v>
+        <v>252.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3448</v>
+      </c>
+      <c r="L17" t="n">
+        <v>121</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:56.174</t>
+          <t>2026-05-29 09:35:57.861</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421738140</v>
+        <v>1780022154612</v>
       </c>
       <c r="C18" t="n">
-        <v>89325</v>
+        <v>85945</v>
       </c>
       <c r="D18" t="n">
-        <v>-90.52</v>
+        <v>1820.15</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>846</v>
+        <v>21410</v>
       </c>
       <c r="G18" t="n">
-        <v>125.67</v>
+        <v>252.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3246</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.354</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:56.175</t>
+          <t>2026-05-29 09:35:57.862</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421738341</v>
+        <v>1780022154812</v>
       </c>
       <c r="C19" t="n">
-        <v>88496</v>
+        <v>86493</v>
       </c>
       <c r="D19" t="n">
-        <v>-914.99</v>
+        <v>2277.14</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>846</v>
+        <v>21410</v>
       </c>
       <c r="G19" t="n">
-        <v>125.67</v>
+        <v>252.6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3049</v>
+      </c>
+      <c r="L19" t="n">
+        <v>111</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:56.593</t>
+          <t>2026-05-29 09:35:57.870</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421738543</v>
+        <v>1780022155012</v>
       </c>
       <c r="C20" t="n">
-        <v>88106</v>
+        <v>86995</v>
       </c>
       <c r="D20" t="n">
-        <v>-1259.24</v>
+        <v>2665.28</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>846</v>
+        <v>21410</v>
       </c>
       <c r="G20" t="n">
-        <v>125.67</v>
+        <v>252.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2856</v>
+      </c>
+      <c r="L20" t="n">
+        <v>109</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:56.594</t>
+          <t>2026-05-29 09:35:57.872</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421738744</v>
+        <v>1780022155212</v>
       </c>
       <c r="C21" t="n">
-        <v>88034</v>
+        <v>86859</v>
       </c>
       <c r="D21" t="n">
-        <v>-1268.28</v>
+        <v>2396.02</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>846</v>
+        <v>21410</v>
       </c>
       <c r="G21" t="n">
-        <v>125.67</v>
+        <v>252.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2659</v>
+      </c>
+      <c r="L21" t="n">
+        <v>101</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.040</t>
+          <t>2026-05-29 09:35:57.874</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421738946</v>
+        <v>1780022155412</v>
       </c>
       <c r="C22" t="n">
-        <v>88451</v>
+        <v>85513</v>
       </c>
       <c r="D22" t="n">
-        <v>-787.87</v>
+        <v>930.22</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
-        <v>846</v>
+        <v>21410</v>
       </c>
       <c r="G22" t="n">
-        <v>125.67</v>
+        <v>252.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2461</v>
+      </c>
+      <c r="L22" t="n">
+        <v>121</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.046</t>
+          <t>2026-05-29 09:35:58.028</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421739147</v>
+        <v>1780022155612</v>
       </c>
       <c r="C23" t="n">
-        <v>88120</v>
+        <v>85118</v>
       </c>
       <c r="D23" t="n">
-        <v>-1079.47</v>
+        <v>488.71</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>1088</v>
+        <v>21410</v>
       </c>
       <c r="G23" t="n">
-        <v>153.48</v>
+        <v>252.6</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2415</v>
+      </c>
+      <c r="L23" t="n">
+        <v>124</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.326</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.424</t>
+          <t>2026-05-29 09:35:58.030</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421739348</v>
+        <v>1780022155812</v>
       </c>
       <c r="C24" t="n">
-        <v>88406</v>
+        <v>84732</v>
       </c>
       <c r="D24" t="n">
-        <v>-739.5</v>
+        <v>78.27</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>1088</v>
+        <v>21410</v>
       </c>
       <c r="G24" t="n">
-        <v>153.48</v>
+        <v>252.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2217</v>
+      </c>
+      <c r="L24" t="n">
+        <v>112</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.432</t>
+          <t>2026-05-29 09:35:58.031</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421739550</v>
+        <v>1780022156012</v>
       </c>
       <c r="C25" t="n">
-        <v>88554</v>
+        <v>84862</v>
       </c>
       <c r="D25" t="n">
-        <v>-554.53</v>
+        <v>204.36</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>402</v>
+        <v>21410</v>
       </c>
       <c r="G25" t="n">
-        <v>191.32</v>
+        <v>252.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L25" t="n">
+        <v>114</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.871</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.806</t>
+          <t>2026-05-29 09:35:58.032</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421739751</v>
+        <v>1780022156212</v>
       </c>
       <c r="C26" t="n">
-        <v>88717</v>
+        <v>85269</v>
       </c>
       <c r="D26" t="n">
-        <v>-363.8</v>
+        <v>601.14</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>402</v>
+        <v>21410</v>
       </c>
       <c r="G26" t="n">
-        <v>191.32</v>
+        <v>252.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1819</v>
+      </c>
+      <c r="L26" t="n">
+        <v>120</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.013</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:57.818</t>
+          <t>2026-05-29 09:36:00.098</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421739953</v>
+        <v>1780022156412</v>
       </c>
       <c r="C27" t="n">
-        <v>88304</v>
+        <v>85245</v>
       </c>
       <c r="D27" t="n">
-        <v>-758.61</v>
+        <v>547.08</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>402</v>
+        <v>21410</v>
       </c>
       <c r="G27" t="n">
-        <v>191.32</v>
+        <v>252.6</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3685</v>
+      </c>
+      <c r="L27" t="n">
+        <v>112</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.211</t>
+          <t>2026-05-29 09:36:00.108</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421740154</v>
+        <v>1780022156612</v>
       </c>
       <c r="C28" t="n">
-        <v>88618</v>
+        <v>85327</v>
       </c>
       <c r="D28" t="n">
-        <v>-406.68</v>
+        <v>601.73</v>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>402</v>
+        <v>21410</v>
       </c>
       <c r="G28" t="n">
-        <v>191.32</v>
+        <v>252.6</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3495</v>
+      </c>
+      <c r="L28" t="n">
+        <v>120</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.049</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.212</t>
+          <t>2026-05-29 09:36:00.139</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421740355</v>
+        <v>1780022156812</v>
       </c>
       <c r="C29" t="n">
-        <v>88908</v>
+        <v>88160</v>
       </c>
       <c r="D29" t="n">
-        <v>-96.34</v>
+        <v>3404.64</v>
       </c>
       <c r="E29" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F29" t="n">
-        <v>746</v>
+        <v>21410</v>
       </c>
       <c r="G29" t="n">
-        <v>180.24</v>
+        <v>252.6</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3326</v>
+      </c>
+      <c r="L29" t="n">
+        <v>120</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.481</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.726</t>
+          <t>2026-05-29 09:36:00.511</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421740557</v>
+        <v>1780022157031</v>
       </c>
       <c r="C30" t="n">
-        <v>88858</v>
+        <v>89091</v>
       </c>
       <c r="D30" t="n">
-        <v>-141.53</v>
+        <v>4165.41</v>
       </c>
       <c r="E30" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>746</v>
+        <v>21410</v>
       </c>
       <c r="G30" t="n">
-        <v>180.24</v>
+        <v>252.6</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3479</v>
+      </c>
+      <c r="L30" t="n">
+        <v>116</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.057</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.733</t>
+          <t>2026-05-29 09:36:00.513</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421740758</v>
+        <v>1780022159350</v>
       </c>
       <c r="C31" t="n">
-        <v>88496</v>
+        <v>86320</v>
       </c>
       <c r="D31" t="n">
-        <v>-496.45</v>
+        <v>1186.14</v>
       </c>
       <c r="E31" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F31" t="n">
-        <v>746</v>
+        <v>21410</v>
       </c>
       <c r="G31" t="n">
-        <v>180.24</v>
+        <v>252.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L31" t="n">
+        <v>124</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.947</t>
+          <t>2026-05-29 09:36:00.514</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421740960</v>
+        <v>1780022159550</v>
       </c>
       <c r="C32" t="n">
-        <v>88730</v>
+        <v>86191</v>
       </c>
       <c r="D32" t="n">
-        <v>-237.63</v>
+        <v>997.83</v>
       </c>
       <c r="E32" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F32" t="n">
-        <v>746</v>
+        <v>21410</v>
       </c>
       <c r="G32" t="n">
-        <v>180.24</v>
+        <v>252.6</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>963</v>
+      </c>
+      <c r="L32" t="n">
+        <v>120</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.389</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:58.948</t>
+          <t>2026-05-29 09:36:00.515</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421741161</v>
+        <v>1780022159750</v>
       </c>
       <c r="C33" t="n">
-        <v>88868</v>
+        <v>86152</v>
       </c>
       <c r="D33" t="n">
-        <v>-87.75</v>
+        <v>908.9400000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>866</v>
+        <v>21410</v>
       </c>
       <c r="G33" t="n">
-        <v>175.97</v>
+        <v>252.6</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K33" t="n">
+        <v>764</v>
+      </c>
+      <c r="L33" t="n">
+        <v>117</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.992</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:59.234</t>
+          <t>2026-05-29 09:36:01.511</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421741362</v>
+        <v>1780022159950</v>
       </c>
       <c r="C34" t="n">
-        <v>88155</v>
+        <v>86274</v>
       </c>
       <c r="D34" t="n">
-        <v>-796.36</v>
+        <v>985.49</v>
       </c>
       <c r="E34" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F34" t="n">
-        <v>866</v>
+        <v>21410</v>
       </c>
       <c r="G34" t="n">
-        <v>175.97</v>
+        <v>252.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1559</v>
+      </c>
+      <c r="L34" t="n">
+        <v>121</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.153</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:59.711</t>
+          <t>2026-05-29 09:36:02.989</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421741564</v>
+        <v>1780022160151</v>
       </c>
       <c r="C35" t="n">
-        <v>88595</v>
+        <v>86381</v>
       </c>
       <c r="D35" t="n">
-        <v>-316.54</v>
+        <v>1043.22</v>
       </c>
       <c r="E35" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F35" t="n">
-        <v>866</v>
+        <v>21410</v>
       </c>
       <c r="G35" t="n">
-        <v>175.97</v>
+        <v>252.6</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2837</v>
+      </c>
+      <c r="L35" t="n">
+        <v>110</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:59.727</t>
+          <t>2026-05-29 09:36:02.991</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421741765</v>
+        <v>1780022160350</v>
       </c>
       <c r="C36" t="n">
-        <v>89824</v>
+        <v>86564</v>
       </c>
       <c r="D36" t="n">
-        <v>928.29</v>
+        <v>1174.06</v>
       </c>
       <c r="E36" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F36" t="n">
-        <v>644</v>
+        <v>21410</v>
       </c>
       <c r="G36" t="n">
-        <v>179.29</v>
+        <v>252.6</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2640</v>
+      </c>
+      <c r="L36" t="n">
+        <v>126</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.337</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.053</t>
+          <t>2026-05-29 09:36:02.993</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421741967</v>
+        <v>1780022160550</v>
       </c>
       <c r="C37" t="n">
-        <v>88971</v>
+        <v>86523</v>
       </c>
       <c r="D37" t="n">
-        <v>28.87</v>
+        <v>1074.36</v>
       </c>
       <c r="E37" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F37" t="n">
-        <v>644</v>
+        <v>21410</v>
       </c>
       <c r="G37" t="n">
-        <v>179.29</v>
+        <v>252.6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2442</v>
+      </c>
+      <c r="L37" t="n">
+        <v>112</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.201</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.054</t>
+          <t>2026-05-29 09:36:02.994</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421742168</v>
+        <v>1780022160750</v>
       </c>
       <c r="C38" t="n">
-        <v>89349</v>
+        <v>86457</v>
       </c>
       <c r="D38" t="n">
-        <v>405.43</v>
+        <v>954.64</v>
       </c>
       <c r="E38" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F38" t="n">
-        <v>644</v>
+        <v>21410</v>
       </c>
       <c r="G38" t="n">
-        <v>179.29</v>
+        <v>252.6</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2243</v>
+      </c>
+      <c r="L38" t="n">
+        <v>113</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.465</t>
+          <t>2026-05-29 09:36:02.995</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421742369</v>
+        <v>1780022160950</v>
       </c>
       <c r="C39" t="n">
-        <v>89412</v>
+        <v>86482</v>
       </c>
       <c r="D39" t="n">
-        <v>448.16</v>
+        <v>931.91</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F39" t="n">
-        <v>504</v>
+        <v>21410</v>
       </c>
       <c r="G39" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2045</v>
+      </c>
+      <c r="L39" t="n">
+        <v>112</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.714</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.467</t>
+          <t>2026-05-29 09:36:02.996</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421742571</v>
+        <v>1780022161150</v>
       </c>
       <c r="C40" t="n">
-        <v>89515</v>
+        <v>86556</v>
       </c>
       <c r="D40" t="n">
-        <v>528.75</v>
+        <v>959.3099999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F40" t="n">
-        <v>504</v>
+        <v>7797</v>
       </c>
       <c r="G40" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1845</v>
+      </c>
+      <c r="L40" t="n">
+        <v>109</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.893</t>
+          <t>2026-05-29 09:36:02.998</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421742772</v>
+        <v>1780022161350</v>
       </c>
       <c r="C41" t="n">
-        <v>89070</v>
+        <v>86545</v>
       </c>
       <c r="D41" t="n">
-        <v>57.31</v>
+        <v>900.34</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F41" t="n">
-        <v>504</v>
+        <v>7797</v>
       </c>
       <c r="G41" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L41" t="n">
+        <v>109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.995</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:00.894</t>
+          <t>2026-05-29 09:36:02.999</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421742974</v>
+        <v>1780022161550</v>
       </c>
       <c r="C42" t="n">
-        <v>88936</v>
+        <v>86715</v>
       </c>
       <c r="D42" t="n">
-        <v>-79.55</v>
+        <v>1025.33</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>504</v>
+        <v>7797</v>
       </c>
       <c r="G42" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1448</v>
+      </c>
+      <c r="L42" t="n">
+        <v>108</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.865</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:01.280</t>
+          <t>2026-05-29 09:36:03.000</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421743175</v>
+        <v>1780022161750</v>
       </c>
       <c r="C43" t="n">
-        <v>89045</v>
+        <v>86861</v>
       </c>
       <c r="D43" t="n">
-        <v>33.42</v>
+        <v>1120.06</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>504</v>
+        <v>7797</v>
       </c>
       <c r="G43" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L43" t="n">
+        <v>106</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.162</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:01.281</t>
+          <t>2026-05-29 09:36:04.222</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421743377</v>
+        <v>1780022161969</v>
       </c>
       <c r="C44" t="n">
-        <v>89270</v>
+        <v>86858</v>
       </c>
       <c r="D44" t="n">
-        <v>256.75</v>
+        <v>1061.06</v>
       </c>
       <c r="E44" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F44" t="n">
-        <v>504</v>
+        <v>7797</v>
       </c>
       <c r="G44" t="n">
-        <v>193.45</v>
+        <v>252.6</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2252</v>
+      </c>
+      <c r="L44" t="n">
+        <v>118</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:01.718</t>
+          <t>2026-05-29 09:36:04.223</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421743578</v>
+        <v>1780022162209</v>
       </c>
       <c r="C45" t="n">
-        <v>88473</v>
+        <v>86385</v>
       </c>
       <c r="D45" t="n">
-        <v>-553.09</v>
+        <v>535.01</v>
       </c>
       <c r="E45" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F45" t="n">
-        <v>1168</v>
+        <v>7797</v>
       </c>
       <c r="G45" t="n">
-        <v>236.19</v>
+        <v>252.6</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2013</v>
+      </c>
+      <c r="L45" t="n">
+        <v>122</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.726</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:01.720</t>
+          <t>2026-05-29 09:36:04.223</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421743779</v>
+        <v>1780022162409</v>
       </c>
       <c r="C46" t="n">
-        <v>88536</v>
+        <v>86770</v>
       </c>
       <c r="D46" t="n">
-        <v>-462.43</v>
+        <v>893.25</v>
       </c>
       <c r="E46" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F46" t="n">
-        <v>1168</v>
+        <v>7797</v>
       </c>
       <c r="G46" t="n">
-        <v>236.19</v>
+        <v>252.6</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1814</v>
+      </c>
+      <c r="L46" t="n">
+        <v>116</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.478</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:02.239</t>
+          <t>2026-05-29 09:36:04.224</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421743981</v>
+        <v>1780022162609</v>
       </c>
       <c r="C47" t="n">
-        <v>88764</v>
+        <v>87061</v>
       </c>
       <c r="D47" t="n">
-        <v>-211.31</v>
+        <v>1139.59</v>
       </c>
       <c r="E47" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>1168</v>
+        <v>1479</v>
       </c>
       <c r="G47" t="n">
-        <v>236.19</v>
+        <v>333.38</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1614</v>
+      </c>
+      <c r="L47" t="n">
+        <v>109</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.506</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:02.240</t>
+          <t>2026-05-29 09:36:04.638</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421744182</v>
+        <v>1780022162809</v>
       </c>
       <c r="C48" t="n">
-        <v>88976</v>
+        <v>87016</v>
       </c>
       <c r="D48" t="n">
-        <v>11.26</v>
+        <v>1037.61</v>
       </c>
       <c r="E48" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>745</v>
+        <v>1479</v>
       </c>
       <c r="G48" t="n">
-        <v>236.17</v>
+        <v>333.38</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1828</v>
+      </c>
+      <c r="L48" t="n">
+        <v>127</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:02.241</t>
+          <t>2026-05-29 09:36:04.639</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421744384</v>
+        <v>1780022163009</v>
       </c>
       <c r="C49" t="n">
-        <v>88455</v>
+        <v>86518</v>
       </c>
       <c r="D49" t="n">
-        <v>-510.31</v>
+        <v>487.73</v>
       </c>
       <c r="E49" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F49" t="n">
-        <v>745</v>
+        <v>1479</v>
       </c>
       <c r="G49" t="n">
-        <v>236.17</v>
+        <v>333.38</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1629</v>
+      </c>
+      <c r="L49" t="n">
+        <v>109</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.318</t>
+          <t>2026-05-29 09:36:04.640</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421744585</v>
+        <v>1780022163209</v>
       </c>
       <c r="C50" t="n">
-        <v>88529</v>
+        <v>86735</v>
       </c>
       <c r="D50" t="n">
-        <v>-410.79</v>
+        <v>680.35</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F50" t="n">
-        <v>745</v>
+        <v>1479</v>
       </c>
       <c r="G50" t="n">
-        <v>236.17</v>
+        <v>333.38</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1430</v>
+      </c>
+      <c r="L50" t="n">
+        <v>111</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.027</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.331</t>
+          <t>2026-05-29 09:36:04.642</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421744787</v>
+        <v>1780022163409</v>
       </c>
       <c r="C51" t="n">
-        <v>88661</v>
+        <v>88268</v>
       </c>
       <c r="D51" t="n">
-        <v>-258.25</v>
+        <v>2179.33</v>
       </c>
       <c r="E51" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F51" t="n">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="G51" t="n">
-        <v>236.17</v>
+        <v>320.19</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1232</v>
+      </c>
+      <c r="L51" t="n">
+        <v>109</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.332</t>
+          <t>2026-05-29 09:36:06.694</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421744988</v>
+        <v>1780022163609</v>
       </c>
       <c r="C52" t="n">
-        <v>88828</v>
+        <v>89067</v>
       </c>
       <c r="D52" t="n">
-        <v>-78.34</v>
+        <v>2869.36</v>
       </c>
       <c r="E52" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F52" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G52" t="n">
-        <v>235.02</v>
+        <v>320.19</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3084</v>
+      </c>
+      <c r="L52" t="n">
+        <v>102</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.364</t>
+          <t>2026-05-29 09:36:07.137</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421745189</v>
+        <v>1780022163809</v>
       </c>
       <c r="C53" t="n">
-        <v>88255</v>
+        <v>87085</v>
       </c>
       <c r="D53" t="n">
-        <v>-647.42</v>
+        <v>743.89</v>
       </c>
       <c r="E53" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F53" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G53" t="n">
-        <v>235.02</v>
+        <v>320.19</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3326</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.133</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.365</t>
+          <t>2026-05-29 09:36:07.207</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421745391</v>
+        <v>1780022165689</v>
       </c>
       <c r="C54" t="n">
-        <v>88495</v>
+        <v>92432</v>
       </c>
       <c r="D54" t="n">
-        <v>-375.05</v>
+        <v>6053.7</v>
       </c>
       <c r="E54" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F54" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G54" t="n">
-        <v>235.02</v>
+        <v>320.19</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1517</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.603</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.560</t>
+          <t>2026-05-29 09:36:07.208</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421745592</v>
+        <v>1780022165908</v>
       </c>
       <c r="C55" t="n">
-        <v>88713</v>
+        <v>89033</v>
       </c>
       <c r="D55" t="n">
-        <v>-138.3</v>
+        <v>2352.01</v>
       </c>
       <c r="E55" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F55" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G55" t="n">
-        <v>235.02</v>
+        <v>320.19</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L55" t="n">
+        <v>108</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.618</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.565</t>
+          <t>2026-05-29 09:36:07.229</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421745794</v>
+        <v>1780022166108</v>
       </c>
       <c r="C56" t="n">
-        <v>88907</v>
+        <v>88577</v>
       </c>
       <c r="D56" t="n">
-        <v>62.62</v>
+        <v>1778.41</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F56" t="n">
-        <v>705</v>
+        <v>800</v>
       </c>
       <c r="G56" t="n">
-        <v>234.82</v>
+        <v>320.19</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L56" t="n">
+        <v>108</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.082</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.957</t>
+          <t>2026-05-29 09:36:08.516</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421745995</v>
+        <v>1780022166308</v>
       </c>
       <c r="C57" t="n">
-        <v>88149</v>
+        <v>87622</v>
       </c>
       <c r="D57" t="n">
-        <v>-698.51</v>
+        <v>734.49</v>
       </c>
       <c r="E57" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F57" t="n">
-        <v>705</v>
+        <v>800</v>
       </c>
       <c r="G57" t="n">
-        <v>234.82</v>
+        <v>320.19</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2207</v>
+      </c>
+      <c r="L57" t="n">
+        <v>107</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.221</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:03.959</t>
+          <t>2026-05-29 09:36:08.518</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421746196</v>
+        <v>1780022166508</v>
       </c>
       <c r="C58" t="n">
-        <v>88402</v>
+        <v>88339</v>
       </c>
       <c r="D58" t="n">
-        <v>-410.59</v>
+        <v>1414.77</v>
       </c>
       <c r="E58" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F58" t="n">
-        <v>705</v>
+        <v>800</v>
       </c>
       <c r="G58" t="n">
-        <v>234.82</v>
+        <v>320.19</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L58" t="n">
+        <v>108</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:04.567</t>
+          <t>2026-05-29 09:36:08.520</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421746398</v>
+        <v>1780022166727</v>
       </c>
       <c r="C59" t="n">
-        <v>88603</v>
+        <v>87991</v>
       </c>
       <c r="D59" t="n">
-        <v>-189.06</v>
+        <v>996.03</v>
       </c>
       <c r="E59" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F59" t="n">
-        <v>705</v>
+        <v>800</v>
       </c>
       <c r="G59" t="n">
-        <v>234.82</v>
+        <v>320.19</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1792</v>
+      </c>
+      <c r="L59" t="n">
+        <v>106</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:04.568</t>
+          <t>2026-05-29 09:36:08.757</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421746599</v>
+        <v>1780022166927</v>
       </c>
       <c r="C60" t="n">
-        <v>88840</v>
+        <v>88562</v>
       </c>
       <c r="D60" t="n">
-        <v>57.39</v>
+        <v>1517.23</v>
       </c>
       <c r="E60" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F60" t="n">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="G60" t="n">
-        <v>208.92</v>
+        <v>320.19</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1830</v>
+      </c>
+      <c r="L60" t="n">
+        <v>106</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:04.569</t>
+          <t>2026-05-29 09:36:08.763</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421746801</v>
+        <v>1780022167127</v>
       </c>
       <c r="C61" t="n">
-        <v>88241</v>
+        <v>88284</v>
       </c>
       <c r="D61" t="n">
-        <v>-544.48</v>
+        <v>1163.37</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F61" t="n">
-        <v>846</v>
+        <v>3658</v>
       </c>
       <c r="G61" t="n">
-        <v>208.92</v>
+        <v>320.19</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1635</v>
+      </c>
+      <c r="L61" t="n">
+        <v>109</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.826</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:04.970</t>
+          <t>2026-05-29 09:36:08.764</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421747002</v>
+        <v>1780022167327</v>
       </c>
       <c r="C62" t="n">
-        <v>88449</v>
+        <v>88098</v>
       </c>
       <c r="D62" t="n">
-        <v>-309.25</v>
+        <v>919.2</v>
       </c>
       <c r="E62" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F62" t="n">
-        <v>846</v>
+        <v>3658</v>
       </c>
       <c r="G62" t="n">
-        <v>208.92</v>
+        <v>320.19</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1436</v>
+      </c>
+      <c r="L62" t="n">
+        <v>116</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:04.994</t>
+          <t>2026-05-29 09:36:10.336</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421747203</v>
+        <v>1780022167528</v>
       </c>
       <c r="C63" t="n">
-        <v>88644</v>
+        <v>86292</v>
       </c>
       <c r="D63" t="n">
-        <v>-98.79000000000001</v>
+        <v>-932.76</v>
       </c>
       <c r="E63" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F63" t="n">
-        <v>846</v>
+        <v>3658</v>
       </c>
       <c r="G63" t="n">
-        <v>208.92</v>
+        <v>320.19</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2806</v>
+      </c>
+      <c r="L63" t="n">
+        <v>106</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:05.377</t>
+          <t>2026-05-29 09:36:10.337</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421747405</v>
+        <v>1780022167727</v>
       </c>
       <c r="C64" t="n">
-        <v>88829</v>
+        <v>87108</v>
       </c>
       <c r="D64" t="n">
-        <v>91.15000000000001</v>
+        <v>-70.12</v>
       </c>
       <c r="E64" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F64" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G64" t="n">
-        <v>171.65</v>
+        <v>320.19</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2609</v>
+      </c>
+      <c r="L64" t="n">
+        <v>121</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.289</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:05.378</t>
+          <t>2026-05-29 09:36:10.342</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421747606</v>
+        <v>1780022167927</v>
       </c>
       <c r="C65" t="n">
-        <v>88277</v>
+        <v>87669</v>
       </c>
       <c r="D65" t="n">
-        <v>-465.41</v>
+        <v>494.38</v>
       </c>
       <c r="E65" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F65" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G65" t="n">
-        <v>171.65</v>
+        <v>320.19</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2414</v>
+      </c>
+      <c r="L65" t="n">
+        <v>112</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.165</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:05.808</t>
+          <t>2026-05-29 09:36:10.552</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421747808</v>
+        <v>1780022168128</v>
       </c>
       <c r="C66" t="n">
-        <v>88473</v>
+        <v>87798</v>
       </c>
       <c r="D66" t="n">
-        <v>-246.14</v>
+        <v>598.66</v>
       </c>
       <c r="E66" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F66" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G66" t="n">
-        <v>171.65</v>
+        <v>320.19</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2423</v>
+      </c>
+      <c r="L66" t="n">
+        <v>113</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.739</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:05.809</t>
+          <t>2026-05-29 09:36:10.553</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421748009</v>
+        <v>1780022168327</v>
       </c>
       <c r="C67" t="n">
-        <v>88700</v>
+        <v>88206</v>
       </c>
       <c r="D67" t="n">
-        <v>-6.83</v>
+        <v>976.73</v>
       </c>
       <c r="E67" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F67" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G67" t="n">
-        <v>171.65</v>
+        <v>320.19</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2225</v>
+      </c>
+      <c r="L67" t="n">
+        <v>119</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.608</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:06.633</t>
+          <t>2026-05-29 09:36:10.554</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421748210</v>
+        <v>1780022168527</v>
       </c>
       <c r="C68" t="n">
-        <v>88575</v>
+        <v>88651</v>
       </c>
       <c r="D68" t="n">
-        <v>-131.49</v>
+        <v>1372.89</v>
       </c>
       <c r="E68" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F68" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G68" t="n">
-        <v>171.37</v>
+        <v>320.19</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L68" t="n">
+        <v>107</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:06.634</t>
+          <t>2026-05-29 09:36:10.554</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421748412</v>
+        <v>1780022168727</v>
       </c>
       <c r="C69" t="n">
-        <v>88348</v>
+        <v>89200</v>
       </c>
       <c r="D69" t="n">
-        <v>-351.91</v>
+        <v>1853.25</v>
       </c>
       <c r="E69" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F69" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G69" t="n">
-        <v>171.37</v>
+        <v>320.19</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1827</v>
+      </c>
+      <c r="L69" t="n">
+        <v>95</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:06.636</t>
+          <t>2026-05-29 09:36:10.558</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421748613</v>
+        <v>1780022168927</v>
       </c>
       <c r="C70" t="n">
-        <v>88515</v>
+        <v>89164</v>
       </c>
       <c r="D70" t="n">
-        <v>-167.32</v>
+        <v>1724.59</v>
       </c>
       <c r="E70" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F70" t="n">
-        <v>765</v>
+        <v>3658</v>
       </c>
       <c r="G70" t="n">
-        <v>171.37</v>
+        <v>320.19</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1630</v>
+      </c>
+      <c r="L70" t="n">
+        <v>113</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.077</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:06.636</t>
+          <t>2026-05-29 09:36:10.559</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421748815</v>
+        <v>1780022169147</v>
       </c>
       <c r="C71" t="n">
-        <v>88763</v>
+        <v>89131</v>
       </c>
       <c r="D71" t="n">
-        <v>89.05</v>
+        <v>1605.36</v>
       </c>
       <c r="E71" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F71" t="n">
-        <v>725</v>
+        <v>3658</v>
       </c>
       <c r="G71" t="n">
-        <v>169.24</v>
+        <v>320.19</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J71" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1411</v>
+      </c>
+      <c r="L71" t="n">
+        <v>106</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.151</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:07.032</t>
+          <t>2026-05-29 09:36:11.823</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421749016</v>
+        <v>1780022169346</v>
       </c>
       <c r="C72" t="n">
-        <v>88192</v>
+        <v>88595</v>
       </c>
       <c r="D72" t="n">
-        <v>-486.41</v>
+        <v>989.09</v>
       </c>
       <c r="E72" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F72" t="n">
-        <v>725</v>
+        <v>3658</v>
       </c>
       <c r="G72" t="n">
-        <v>169.24</v>
+        <v>320.19</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J72" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2476</v>
+      </c>
+      <c r="L72" t="n">
+        <v>106</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:07.034</t>
+          <t>2026-05-29 09:36:11.838</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421749217</v>
+        <v>1780022169546</v>
       </c>
       <c r="C73" t="n">
-        <v>88347</v>
+        <v>87777</v>
       </c>
       <c r="D73" t="n">
-        <v>-307.08</v>
+        <v>121.64</v>
       </c>
       <c r="E73" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F73" t="n">
-        <v>725</v>
+        <v>3658</v>
       </c>
       <c r="G73" t="n">
-        <v>169.24</v>
+        <v>320.19</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2292</v>
+      </c>
+      <c r="L73" t="n">
+        <v>117</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.635</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:07.459</t>
+          <t>2026-05-29 09:36:11.848</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421749419</v>
+        <v>1780022169746</v>
       </c>
       <c r="C74" t="n">
-        <v>88516</v>
+        <v>88125</v>
       </c>
       <c r="D74" t="n">
-        <v>-122.73</v>
+        <v>463.55</v>
       </c>
       <c r="E74" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F74" t="n">
-        <v>725</v>
+        <v>3658</v>
       </c>
       <c r="G74" t="n">
-        <v>169.24</v>
+        <v>320.19</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2102</v>
+      </c>
+      <c r="L74" t="n">
+        <v>125</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.579</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:07.481</t>
+          <t>2026-05-29 09:36:11.850</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421749620</v>
+        <v>1780022169946</v>
       </c>
       <c r="C75" t="n">
-        <v>88748</v>
+        <v>87602</v>
       </c>
       <c r="D75" t="n">
-        <v>115.41</v>
+        <v>-82.62</v>
       </c>
       <c r="E75" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F75" t="n">
-        <v>766</v>
+        <v>3658</v>
       </c>
       <c r="G75" t="n">
-        <v>163.83</v>
+        <v>320.19</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1903</v>
+      </c>
+      <c r="L75" t="n">
+        <v>113</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.486</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.349</t>
+          <t>2026-05-29 09:36:11.853</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421749822</v>
+        <v>1780022170146</v>
       </c>
       <c r="C76" t="n">
-        <v>88270</v>
+        <v>87369</v>
       </c>
       <c r="D76" t="n">
-        <v>-368.36</v>
+        <v>-311.49</v>
       </c>
       <c r="E76" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F76" t="n">
-        <v>766</v>
+        <v>3658</v>
       </c>
       <c r="G76" t="n">
-        <v>163.83</v>
+        <v>320.19</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1706</v>
+      </c>
+      <c r="L76" t="n">
+        <v>114</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.350</t>
+          <t>2026-05-29 09:36:12.200</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421750023</v>
+        <v>1780022170346</v>
       </c>
       <c r="C77" t="n">
-        <v>88428</v>
+        <v>87256</v>
       </c>
       <c r="D77" t="n">
-        <v>-191.95</v>
+        <v>-408.92</v>
       </c>
       <c r="E77" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F77" t="n">
-        <v>766</v>
+        <v>3658</v>
       </c>
       <c r="G77" t="n">
-        <v>163.83</v>
+        <v>320.19</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1852</v>
+      </c>
+      <c r="L77" t="n">
+        <v>113</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.582</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.351</t>
+          <t>2026-05-29 09:36:12.336</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421750224</v>
+        <v>1780022170546</v>
       </c>
       <c r="C78" t="n">
-        <v>88606</v>
+        <v>87660</v>
       </c>
       <c r="D78" t="n">
-        <v>-4.35</v>
+        <v>15.53</v>
       </c>
       <c r="E78" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F78" t="n">
-        <v>766</v>
+        <v>3658</v>
       </c>
       <c r="G78" t="n">
-        <v>163.83</v>
+        <v>320.19</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1789</v>
+      </c>
+      <c r="L78" t="n">
+        <v>111</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.172</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.352</t>
+          <t>2026-05-29 09:36:12.352</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421750426</v>
+        <v>1780022170746</v>
       </c>
       <c r="C79" t="n">
-        <v>88790</v>
+        <v>87911</v>
       </c>
       <c r="D79" t="n">
-        <v>179.87</v>
+        <v>265.75</v>
       </c>
       <c r="E79" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F79" t="n">
-        <v>785</v>
+        <v>3658</v>
       </c>
       <c r="G79" t="n">
-        <v>132.89</v>
+        <v>320.19</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1604</v>
+      </c>
+      <c r="L79" t="n">
+        <v>108</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.285</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.668</t>
+          <t>2026-05-29 09:36:12.361</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421750627</v>
+        <v>1780022170946</v>
       </c>
       <c r="C80" t="n">
-        <v>88420</v>
+        <v>87803</v>
       </c>
       <c r="D80" t="n">
-        <v>-199.12</v>
+        <v>144.46</v>
       </c>
       <c r="E80" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F80" t="n">
-        <v>785</v>
+        <v>3658</v>
       </c>
       <c r="G80" t="n">
-        <v>132.89</v>
+        <v>320.19</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1414</v>
+      </c>
+      <c r="L80" t="n">
+        <v>109</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:08.689</t>
+          <t>2026-05-29 09:36:12.370</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421750829</v>
+        <v>1780022171146</v>
       </c>
       <c r="C81" t="n">
-        <v>88574</v>
+        <v>87580</v>
       </c>
       <c r="D81" t="n">
-        <v>-35.17</v>
+        <v>-85.76000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F81" t="n">
-        <v>785</v>
+        <v>3658</v>
       </c>
       <c r="G81" t="n">
-        <v>132.89</v>
+        <v>320.19</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1223</v>
+      </c>
+      <c r="L81" t="n">
+        <v>103</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.543</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:09.080</t>
+          <t>2026-05-29 09:36:12.932</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421751030</v>
+        <v>1780022171365</v>
       </c>
       <c r="C82" t="n">
-        <v>88727</v>
+        <v>87925</v>
       </c>
       <c r="D82" t="n">
-        <v>119.59</v>
+        <v>263.53</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F82" t="n">
-        <v>785</v>
+        <v>3658</v>
       </c>
       <c r="G82" t="n">
-        <v>132.89</v>
+        <v>320.19</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1566</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.344</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:09.081</t>
+          <t>2026-05-29 09:36:12.934</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421751231</v>
+        <v>1780022171565</v>
       </c>
       <c r="C83" t="n">
-        <v>88952</v>
+        <v>87921</v>
       </c>
       <c r="D83" t="n">
-        <v>338.61</v>
+        <v>246.35</v>
       </c>
       <c r="E83" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F83" t="n">
-        <v>786</v>
+        <v>4378</v>
       </c>
       <c r="G83" t="n">
-        <v>38.57</v>
+        <v>320.19</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1368</v>
+      </c>
+      <c r="L83" t="n">
+        <v>115</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.886</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:09.495</t>
+          <t>2026-05-29 09:36:12.935</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421751433</v>
+        <v>1780022171765</v>
       </c>
       <c r="C84" t="n">
-        <v>88816</v>
+        <v>87563</v>
       </c>
       <c r="D84" t="n">
-        <v>185.68</v>
+        <v>-123.97</v>
       </c>
       <c r="E84" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F84" t="n">
-        <v>786</v>
+        <v>4378</v>
       </c>
       <c r="G84" t="n">
-        <v>38.57</v>
+        <v>320.19</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1169</v>
+      </c>
+      <c r="L84" t="n">
+        <v>115</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.766</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:09.519</t>
+          <t>2026-05-29 09:36:12.942</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421751634</v>
+        <v>1780022171965</v>
       </c>
       <c r="C85" t="n">
-        <v>88609</v>
+        <v>87536</v>
       </c>
       <c r="D85" t="n">
-        <v>-30.6</v>
+        <v>-144.77</v>
       </c>
       <c r="E85" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F85" t="n">
-        <v>786</v>
+        <v>4378</v>
       </c>
       <c r="G85" t="n">
-        <v>38.57</v>
+        <v>320.19</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K85" t="n">
+        <v>976</v>
+      </c>
+      <c r="L85" t="n">
+        <v>107</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.515</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.292</t>
+          <t>2026-05-29 09:36:13.348</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421751836</v>
+        <v>1780022172165</v>
       </c>
       <c r="C86" t="n">
-        <v>88755</v>
+        <v>87621</v>
       </c>
       <c r="D86" t="n">
-        <v>116.93</v>
+        <v>-52.53</v>
       </c>
       <c r="E86" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F86" t="n">
-        <v>786</v>
+        <v>4378</v>
       </c>
       <c r="G86" t="n">
-        <v>38.57</v>
+        <v>320.19</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L86" t="n">
+        <v>117</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.293</t>
+          <t>2026-05-29 09:36:13.351</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421752037</v>
+        <v>1780022172365</v>
       </c>
       <c r="C87" t="n">
-        <v>88956</v>
+        <v>87003</v>
       </c>
       <c r="D87" t="n">
-        <v>312.08</v>
+        <v>-667.9</v>
       </c>
       <c r="E87" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F87" t="n">
-        <v>886</v>
+        <v>4378</v>
       </c>
       <c r="G87" t="n">
-        <v>52.67</v>
+        <v>320.19</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K87" t="n">
+        <v>984</v>
+      </c>
+      <c r="L87" t="n">
+        <v>116</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.915</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.294</t>
+          <t>2026-05-29 09:36:13.352</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421752238</v>
+        <v>1780022172565</v>
       </c>
       <c r="C88" t="n">
-        <v>89131</v>
+        <v>87445</v>
       </c>
       <c r="D88" t="n">
-        <v>471.48</v>
+        <v>-192.51</v>
       </c>
       <c r="E88" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F88" t="n">
-        <v>886</v>
+        <v>4378</v>
       </c>
       <c r="G88" t="n">
-        <v>52.67</v>
+        <v>320.19</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K88" t="n">
+        <v>786</v>
+      </c>
+      <c r="L88" t="n">
+        <v>107</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.579</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.295</t>
+          <t>2026-05-29 09:36:14.141</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421752440</v>
+        <v>1780022172765</v>
       </c>
       <c r="C89" t="n">
-        <v>88577</v>
+        <v>87569</v>
       </c>
       <c r="D89" t="n">
-        <v>-106.1</v>
+        <v>-58.88</v>
       </c>
       <c r="E89" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F89" t="n">
-        <v>886</v>
+        <v>1300</v>
       </c>
       <c r="G89" t="n">
-        <v>52.67</v>
+        <v>342.12</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L89" t="n">
+        <v>114</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.763</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.707</t>
+          <t>2026-05-29 09:36:14.142</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421752641</v>
+        <v>1780022172965</v>
       </c>
       <c r="C90" t="n">
-        <v>88759</v>
+        <v>86693</v>
       </c>
       <c r="D90" t="n">
-        <v>81.20999999999999</v>
+        <v>-931.9400000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F90" t="n">
-        <v>886</v>
+        <v>1300</v>
       </c>
       <c r="G90" t="n">
-        <v>52.67</v>
+        <v>342.12</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L90" t="n">
+        <v>110</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.058</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:10.707</t>
+          <t>2026-05-29 09:36:16.530</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421752843</v>
+        <v>1780022173165</v>
       </c>
       <c r="C91" t="n">
-        <v>88921</v>
+        <v>87462</v>
       </c>
       <c r="D91" t="n">
-        <v>239.15</v>
+        <v>-116.34</v>
       </c>
       <c r="E91" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F91" t="n">
-        <v>886</v>
+        <v>1300</v>
       </c>
       <c r="G91" t="n">
-        <v>52.67</v>
+        <v>342.12</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3364</v>
+      </c>
+      <c r="L91" t="n">
+        <v>114</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:11.317</t>
+          <t>2026-05-29 09:36:16.531</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421753044</v>
+        <v>1780022173365</v>
       </c>
       <c r="C92" t="n">
-        <v>89087</v>
+        <v>87086</v>
       </c>
       <c r="D92" t="n">
-        <v>393.19</v>
+        <v>-486.52</v>
       </c>
       <c r="E92" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F92" t="n">
-        <v>926</v>
+        <v>580</v>
       </c>
       <c r="G92" t="n">
-        <v>69.81</v>
+        <v>331.97</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3166</v>
+      </c>
+      <c r="L92" t="n">
+        <v>107</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.525</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:11.324</t>
+          <t>2026-05-29 09:36:16.532</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421753245</v>
+        <v>1780022173584</v>
       </c>
       <c r="C93" t="n">
-        <v>88800</v>
+        <v>86877</v>
       </c>
       <c r="D93" t="n">
-        <v>86.53</v>
+        <v>-671.2</v>
       </c>
       <c r="E93" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F93" t="n">
-        <v>926</v>
+        <v>580</v>
       </c>
       <c r="G93" t="n">
-        <v>69.81</v>
+        <v>331.97</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2947</v>
+      </c>
+      <c r="L93" t="n">
+        <v>108</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.453</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:11.353</t>
+          <t>2026-05-29 09:36:16.532</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421753447</v>
+        <v>1780022173784</v>
       </c>
       <c r="C94" t="n">
-        <v>88728</v>
+        <v>86922</v>
       </c>
       <c r="D94" t="n">
-        <v>10.2</v>
+        <v>-592.64</v>
       </c>
       <c r="E94" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F94" t="n">
-        <v>926</v>
+        <v>580</v>
       </c>
       <c r="G94" t="n">
-        <v>69.81</v>
+        <v>331.97</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2748</v>
+      </c>
+      <c r="L94" t="n">
+        <v>111</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.468</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.043</t>
+          <t>2026-05-29 09:36:17.236</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421753648</v>
+        <v>1780022173984</v>
       </c>
       <c r="C95" t="n">
-        <v>88810</v>
+        <v>87321</v>
       </c>
       <c r="D95" t="n">
-        <v>91.69</v>
+        <v>-164.01</v>
       </c>
       <c r="E95" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F95" t="n">
-        <v>926</v>
+        <v>580</v>
       </c>
       <c r="G95" t="n">
-        <v>69.81</v>
+        <v>331.97</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3251</v>
+      </c>
+      <c r="L95" t="n">
+        <v>104</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.044</t>
+          <t>2026-05-29 09:36:17.245</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421753850</v>
+        <v>1780022174184</v>
       </c>
       <c r="C96" t="n">
-        <v>89021</v>
+        <v>87481</v>
       </c>
       <c r="D96" t="n">
-        <v>298.11</v>
+        <v>4.19</v>
       </c>
       <c r="E96" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F96" t="n">
-        <v>926</v>
+        <v>719</v>
       </c>
       <c r="G96" t="n">
-        <v>69.81</v>
+        <v>332.04</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3060</v>
+      </c>
+      <c r="L96" t="n">
+        <v>105</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.511</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.044</t>
+          <t>2026-05-29 09:36:17.253</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421754051</v>
+        <v>1780022174384</v>
       </c>
       <c r="C97" t="n">
-        <v>88912</v>
+        <v>87668</v>
       </c>
       <c r="D97" t="n">
-        <v>174.2</v>
+        <v>190.98</v>
       </c>
       <c r="E97" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F97" t="n">
-        <v>947</v>
+        <v>719</v>
       </c>
       <c r="G97" t="n">
-        <v>76.56999999999999</v>
+        <v>332.04</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K97" t="n">
+        <v>2868</v>
+      </c>
+      <c r="L97" t="n">
+        <v>107</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.729</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.074</t>
+          <t>2026-05-29 09:36:17.289</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421754252</v>
+        <v>1780022174584</v>
       </c>
       <c r="C98" t="n">
-        <v>88893</v>
+        <v>86434</v>
       </c>
       <c r="D98" t="n">
-        <v>146.49</v>
+        <v>-1052.56</v>
       </c>
       <c r="E98" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F98" t="n">
-        <v>947</v>
+        <v>719</v>
       </c>
       <c r="G98" t="n">
-        <v>76.56999999999999</v>
+        <v>332.04</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K98" t="n">
+        <v>2704</v>
+      </c>
+      <c r="L98" t="n">
+        <v>105</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.350</t>
+          <t>2026-05-29 09:36:17.291</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421754454</v>
+        <v>1780022175323</v>
       </c>
       <c r="C99" t="n">
-        <v>89069</v>
+        <v>87098</v>
       </c>
       <c r="D99" t="n">
-        <v>315.17</v>
+        <v>-335.94</v>
       </c>
       <c r="E99" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F99" t="n">
-        <v>947</v>
+        <v>719</v>
       </c>
       <c r="G99" t="n">
-        <v>76.56999999999999</v>
+        <v>332.04</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1967</v>
+      </c>
+      <c r="L99" t="n">
+        <v>112</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.844</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.778</t>
+          <t>2026-05-29 09:36:17.297</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421754655</v>
+        <v>1780022175523</v>
       </c>
       <c r="C100" t="n">
-        <v>89319</v>
+        <v>86859</v>
       </c>
       <c r="D100" t="n">
-        <v>549.41</v>
+        <v>-558.14</v>
       </c>
       <c r="E100" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F100" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G100" t="n">
-        <v>93.61</v>
+        <v>332.04</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1773</v>
+      </c>
+      <c r="L100" t="n">
+        <v>110</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.246</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:12.779</t>
+          <t>2026-05-29 09:36:17.299</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421754857</v>
+        <v>1780022175723</v>
       </c>
       <c r="C101" t="n">
-        <v>89348</v>
+        <v>86845</v>
       </c>
       <c r="D101" t="n">
-        <v>550.9400000000001</v>
+        <v>-544.23</v>
       </c>
       <c r="E101" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F101" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G101" t="n">
-        <v>93.61</v>
+        <v>332.04</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1574</v>
+      </c>
+      <c r="L101" t="n">
+        <v>106</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.312</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:13.160</t>
+          <t>2026-05-29 09:36:18.588</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421755058</v>
+        <v>1780022175923</v>
       </c>
       <c r="C102" t="n">
-        <v>88836</v>
+        <v>87211</v>
       </c>
       <c r="D102" t="n">
-        <v>11.39</v>
+        <v>-151.02</v>
       </c>
       <c r="E102" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F102" t="n">
-        <v>644</v>
+        <v>719</v>
       </c>
       <c r="G102" t="n">
-        <v>93.61</v>
+        <v>332.04</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2664</v>
+      </c>
+      <c r="L102" t="n">
+        <v>108</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:13.161</t>
+          <t>2026-05-29 09:36:18.595</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421755259</v>
+        <v>1780022176123</v>
       </c>
       <c r="C103" t="n">
-        <v>88986</v>
+        <v>88272</v>
       </c>
       <c r="D103" t="n">
-        <v>160.82</v>
+        <v>917.53</v>
       </c>
       <c r="E103" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F103" t="n">
-        <v>644</v>
+        <v>1999</v>
       </c>
       <c r="G103" t="n">
-        <v>93.61</v>
+        <v>332.04</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J103" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2471</v>
+      </c>
+      <c r="L103" t="n">
+        <v>117</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.148</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:13.722</t>
+          <t>2026-05-29 09:36:19.187</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421755461</v>
+        <v>1780022176323</v>
       </c>
       <c r="C104" t="n">
-        <v>89161</v>
+        <v>87844</v>
       </c>
       <c r="D104" t="n">
-        <v>327.78</v>
+        <v>443.65</v>
       </c>
       <c r="E104" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F104" t="n">
-        <v>644</v>
+        <v>1999</v>
       </c>
       <c r="G104" t="n">
-        <v>93.61</v>
+        <v>332.04</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2863</v>
+      </c>
+      <c r="L104" t="n">
+        <v>102</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:13.723</t>
+          <t>2026-05-29 09:36:19.188</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421755662</v>
+        <v>1780022177782</v>
       </c>
       <c r="C105" t="n">
-        <v>89324</v>
+        <v>87725</v>
       </c>
       <c r="D105" t="n">
-        <v>474.39</v>
+        <v>302.47</v>
       </c>
       <c r="E105" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F105" t="n">
-        <v>987</v>
+        <v>1999</v>
       </c>
       <c r="G105" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L105" t="n">
+        <v>122</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.958</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.167</t>
+          <t>2026-05-29 09:36:19.190</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421755864</v>
+        <v>1780022177982</v>
       </c>
       <c r="C106" t="n">
-        <v>88681</v>
+        <v>88122</v>
       </c>
       <c r="D106" t="n">
-        <v>-192.33</v>
+        <v>684.35</v>
       </c>
       <c r="E106" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F106" t="n">
-        <v>987</v>
+        <v>1999</v>
       </c>
       <c r="G106" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1207</v>
+      </c>
+      <c r="L106" t="n">
+        <v>112</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.901</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.168</t>
+          <t>2026-05-29 09:36:19.770</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421756065</v>
+        <v>1780022178182</v>
       </c>
       <c r="C107" t="n">
-        <v>88781</v>
+        <v>87820</v>
       </c>
       <c r="D107" t="n">
-        <v>-82.70999999999999</v>
+        <v>348.13</v>
       </c>
       <c r="E107" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F107" t="n">
-        <v>987</v>
+        <v>1999</v>
       </c>
       <c r="G107" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L107" t="n">
+        <v>107</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.169</t>
+          <t>2026-05-29 09:36:19.859</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421756266</v>
+        <v>1780022178382</v>
       </c>
       <c r="C108" t="n">
-        <v>88894</v>
+        <v>87603</v>
       </c>
       <c r="D108" t="n">
-        <v>34.42</v>
+        <v>113.72</v>
       </c>
       <c r="E108" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F108" t="n">
-        <v>987</v>
+        <v>1999</v>
       </c>
       <c r="G108" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1476</v>
+      </c>
+      <c r="L108" t="n">
+        <v>118</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.789</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.537</t>
+          <t>2026-05-29 09:36:19.860</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421756468</v>
+        <v>1780022178582</v>
       </c>
       <c r="C109" t="n">
-        <v>88804</v>
+        <v>88017</v>
       </c>
       <c r="D109" t="n">
-        <v>-57.3</v>
+        <v>522.04</v>
       </c>
       <c r="E109" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F109" t="n">
-        <v>987</v>
+        <v>1999</v>
       </c>
       <c r="G109" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L109" t="n">
+        <v>109</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.983</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.551</t>
+          <t>2026-05-29 09:36:20.433</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421756669</v>
+        <v>1780022178801</v>
       </c>
       <c r="C110" t="n">
-        <v>88233</v>
+        <v>89045</v>
       </c>
       <c r="D110" t="n">
-        <v>-625.4299999999999</v>
+        <v>1523.94</v>
       </c>
       <c r="E110" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F110" t="n">
-        <v>987</v>
+        <v>2638</v>
       </c>
       <c r="G110" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1630</v>
+      </c>
+      <c r="L110" t="n">
+        <v>110</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.209</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.796</t>
+          <t>2026-05-29 09:36:20.513</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421756871</v>
+        <v>1780022179001</v>
       </c>
       <c r="C111" t="n">
-        <v>88354</v>
+        <v>88519</v>
       </c>
       <c r="D111" t="n">
-        <v>-473.16</v>
+        <v>921.74</v>
       </c>
       <c r="E111" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F111" t="n">
-        <v>987</v>
+        <v>2638</v>
       </c>
       <c r="G111" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1512</v>
+      </c>
+      <c r="L111" t="n">
+        <v>116</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.643</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:14.797</t>
+          <t>2026-05-29 09:36:20.514</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421757072</v>
+        <v>1780022179201</v>
       </c>
       <c r="C112" t="n">
-        <v>88420</v>
+        <v>89036</v>
       </c>
       <c r="D112" t="n">
-        <v>-383.5</v>
+        <v>1392.65</v>
       </c>
       <c r="E112" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F112" t="n">
-        <v>987</v>
+        <v>2638</v>
       </c>
       <c r="G112" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1313</v>
+      </c>
+      <c r="L112" t="n">
+        <v>113</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:15.212</t>
+          <t>2026-05-29 09:36:21.752</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421757273</v>
+        <v>1780022179402</v>
       </c>
       <c r="C113" t="n">
-        <v>88559</v>
+        <v>88027</v>
       </c>
       <c r="D113" t="n">
-        <v>-225.33</v>
+        <v>314.02</v>
       </c>
       <c r="E113" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F113" t="n">
-        <v>987</v>
+        <v>2638</v>
       </c>
       <c r="G113" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K113" t="n">
+        <v>2349</v>
+      </c>
+      <c r="L113" t="n">
+        <v>106</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:15.237</t>
+          <t>2026-05-29 09:36:21.757</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421757475</v>
+        <v>1780022179601</v>
       </c>
       <c r="C114" t="n">
-        <v>88061</v>
+        <v>87703</v>
       </c>
       <c r="D114" t="n">
-        <v>-712.0599999999999</v>
+        <v>-25.68</v>
       </c>
       <c r="E114" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F114" t="n">
-        <v>1853</v>
+        <v>2638</v>
       </c>
       <c r="G114" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2155</v>
+      </c>
+      <c r="L114" t="n">
+        <v>121</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.013</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:15.738</t>
+          <t>2026-05-29 09:36:21.758</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421757676</v>
+        <v>1780022179801</v>
       </c>
       <c r="C115" t="n">
-        <v>88206</v>
+        <v>87798</v>
       </c>
       <c r="D115" t="n">
-        <v>-531.46</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E115" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F115" t="n">
-        <v>1853</v>
+        <v>2638</v>
       </c>
       <c r="G115" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L115" t="n">
+        <v>109</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:15.739</t>
+          <t>2026-05-29 09:36:21.768</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421757878</v>
+        <v>1780022180002</v>
       </c>
       <c r="C116" t="n">
-        <v>88340</v>
+        <v>88216</v>
       </c>
       <c r="D116" t="n">
-        <v>-370.88</v>
+        <v>485.07</v>
       </c>
       <c r="E116" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F116" t="n">
-        <v>1853</v>
+        <v>2638</v>
       </c>
       <c r="G116" t="n">
-        <v>109.5</v>
+        <v>332.04</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J116" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1766</v>
+      </c>
+      <c r="L116" t="n">
+        <v>126</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.734</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.059</t>
+          <t>2026-05-29 09:36:21.845</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421758079</v>
+        <v>1780022180201</v>
       </c>
       <c r="C117" t="n">
-        <v>88535</v>
+        <v>87805</v>
       </c>
       <c r="D117" t="n">
-        <v>-157.34</v>
+        <v>49.82</v>
       </c>
       <c r="E117" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F117" t="n">
-        <v>685</v>
+        <v>2638</v>
       </c>
       <c r="G117" t="n">
-        <v>116.78</v>
+        <v>332.04</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1642</v>
+      </c>
+      <c r="L117" t="n">
+        <v>121</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.775</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.060</t>
+          <t>2026-05-29 09:36:21.847</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421758280</v>
+        <v>1780022180420</v>
       </c>
       <c r="C118" t="n">
-        <v>87957</v>
+        <v>87981</v>
       </c>
       <c r="D118" t="n">
-        <v>-727.47</v>
+        <v>223.33</v>
       </c>
       <c r="E118" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F118" t="n">
-        <v>685</v>
+        <v>2638</v>
       </c>
       <c r="G118" t="n">
-        <v>116.78</v>
+        <v>332.04</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L118" t="n">
+        <v>113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.139</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.435</t>
+          <t>2026-05-29 09:36:21.848</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421758482</v>
+        <v>1780022180620</v>
       </c>
       <c r="C119" t="n">
-        <v>88110</v>
+        <v>87871</v>
       </c>
       <c r="D119" t="n">
-        <v>-538.1</v>
+        <v>102.16</v>
       </c>
       <c r="E119" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F119" t="n">
-        <v>685</v>
+        <v>1879</v>
       </c>
       <c r="G119" t="n">
-        <v>116.78</v>
+        <v>332.04</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1227</v>
+      </c>
+      <c r="L119" t="n">
+        <v>107</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.037</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.436</t>
+          <t>2026-05-29 09:36:21.850</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421758683</v>
+        <v>1780022180821</v>
       </c>
       <c r="C120" t="n">
-        <v>88262</v>
+        <v>87282</v>
       </c>
       <c r="D120" t="n">
-        <v>-359.19</v>
+        <v>-491.95</v>
       </c>
       <c r="E120" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F120" t="n">
-        <v>685</v>
+        <v>1879</v>
       </c>
       <c r="G120" t="n">
-        <v>116.78</v>
+        <v>332.04</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1028</v>
+      </c>
+      <c r="L120" t="n">
+        <v>106</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.857</t>
+          <t>2026-05-29 09:36:22.365</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421758885</v>
+        <v>1780022181020</v>
       </c>
       <c r="C121" t="n">
-        <v>88497</v>
+        <v>87915</v>
       </c>
       <c r="D121" t="n">
-        <v>-106.24</v>
+        <v>165.65</v>
       </c>
       <c r="E121" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F121" t="n">
-        <v>785</v>
+        <v>1879</v>
       </c>
       <c r="G121" t="n">
-        <v>113.2</v>
+        <v>332.04</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L121" t="n">
+        <v>104</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.463</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:16.858</t>
+          <t>2026-05-29 09:36:22.366</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421759086</v>
+        <v>1780022181220</v>
       </c>
       <c r="C122" t="n">
-        <v>87938</v>
+        <v>88298</v>
       </c>
       <c r="D122" t="n">
-        <v>-659.92</v>
+        <v>540.37</v>
       </c>
       <c r="E122" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F122" t="n">
-        <v>785</v>
+        <v>620</v>
       </c>
       <c r="G122" t="n">
-        <v>113.2</v>
+        <v>341.44</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L122" t="n">
+        <v>107</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:17.322</t>
+          <t>2026-05-29 09:36:22.368</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421759287</v>
+        <v>1780022181420</v>
       </c>
       <c r="C123" t="n">
-        <v>88075</v>
+        <v>88601</v>
       </c>
       <c r="D123" t="n">
-        <v>-489.93</v>
+        <v>816.35</v>
       </c>
       <c r="E123" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F123" t="n">
-        <v>785</v>
+        <v>620</v>
       </c>
       <c r="G123" t="n">
-        <v>113.2</v>
+        <v>341.44</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K123" t="n">
+        <v>947</v>
+      </c>
+      <c r="L123" t="n">
+        <v>105</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:17.323</t>
+          <t>2026-05-29 09:36:22.761</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421759489</v>
+        <v>1780022181620</v>
       </c>
       <c r="C124" t="n">
-        <v>88210</v>
+        <v>88504</v>
       </c>
       <c r="D124" t="n">
-        <v>-330.43</v>
+        <v>678.53</v>
       </c>
       <c r="E124" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F124" t="n">
-        <v>785</v>
+        <v>620</v>
       </c>
       <c r="G124" t="n">
-        <v>113.2</v>
+        <v>341.44</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L124" t="n">
+        <v>108</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:17.680</t>
+          <t>2026-05-29 09:36:22.763</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421759690</v>
+        <v>1780022181820</v>
       </c>
       <c r="C125" t="n">
-        <v>88404</v>
+        <v>88263</v>
       </c>
       <c r="D125" t="n">
-        <v>-119.91</v>
+        <v>403.61</v>
       </c>
       <c r="E125" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F125" t="n">
-        <v>826</v>
+        <v>620</v>
       </c>
       <c r="G125" t="n">
-        <v>111.62</v>
+        <v>341.44</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K125" t="n">
+        <v>942</v>
+      </c>
+      <c r="L125" t="n">
+        <v>107</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.065</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:17.686</t>
+          <t>2026-05-29 09:36:22.764</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421759892</v>
+        <v>1780022182020</v>
       </c>
       <c r="C126" t="n">
-        <v>88186</v>
+        <v>88038</v>
       </c>
       <c r="D126" t="n">
-        <v>-331.91</v>
+        <v>158.43</v>
       </c>
       <c r="E126" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F126" t="n">
-        <v>826</v>
+        <v>620</v>
       </c>
       <c r="G126" t="n">
-        <v>111.62</v>
+        <v>341.44</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K126" t="n">
+        <v>743</v>
+      </c>
+      <c r="L126" t="n">
+        <v>106</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.215</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.110</t>
+          <t>2026-05-29 09:36:23.388</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421760093</v>
+        <v>1780022182239</v>
       </c>
       <c r="C127" t="n">
-        <v>87967</v>
+        <v>88230</v>
       </c>
       <c r="D127" t="n">
-        <v>-534.3200000000001</v>
+        <v>342.5</v>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F127" t="n">
-        <v>826</v>
+        <v>620</v>
       </c>
       <c r="G127" t="n">
-        <v>111.62</v>
+        <v>341.44</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1148</v>
+      </c>
+      <c r="L127" t="n">
+        <v>108</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.118</t>
+          <t>2026-05-29 09:36:23.389</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421760294</v>
+        <v>1780022182439</v>
       </c>
       <c r="C128" t="n">
-        <v>88080</v>
+        <v>88248</v>
       </c>
       <c r="D128" t="n">
-        <v>-394.6</v>
+        <v>343.38</v>
       </c>
       <c r="E128" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F128" t="n">
-        <v>826</v>
+        <v>1259</v>
       </c>
       <c r="G128" t="n">
-        <v>111.62</v>
+        <v>342.73</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>949</v>
+      </c>
+      <c r="L128" t="n">
+        <v>117</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.486</t>
+          <t>2026-05-29 09:36:24.487</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421760496</v>
+        <v>1780022182639</v>
       </c>
       <c r="C129" t="n">
-        <v>88219</v>
+        <v>88150</v>
       </c>
       <c r="D129" t="n">
-        <v>-235.87</v>
+        <v>228.21</v>
       </c>
       <c r="E129" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F129" t="n">
-        <v>826</v>
+        <v>1259</v>
       </c>
       <c r="G129" t="n">
-        <v>111.62</v>
+        <v>342.73</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1848</v>
+      </c>
+      <c r="L129" t="n">
+        <v>114</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.621</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.487</t>
+          <t>2026-05-29 09:36:24.488</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421760697</v>
+        <v>1780022182839</v>
       </c>
       <c r="C130" t="n">
-        <v>88263</v>
+        <v>88194</v>
       </c>
       <c r="D130" t="n">
-        <v>-180.08</v>
+        <v>260.8</v>
       </c>
       <c r="E130" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F130" t="n">
-        <v>886</v>
+        <v>1259</v>
       </c>
       <c r="G130" t="n">
-        <v>112.09</v>
+        <v>342.73</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1648</v>
+      </c>
+      <c r="L130" t="n">
+        <v>108</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.455</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.898</t>
+          <t>2026-05-29 09:36:24.489</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421760899</v>
+        <v>1780022183039</v>
       </c>
       <c r="C131" t="n">
-        <v>87796</v>
+        <v>88224</v>
       </c>
       <c r="D131" t="n">
-        <v>-638.0700000000001</v>
+        <v>277.76</v>
       </c>
       <c r="E131" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F131" t="n">
-        <v>886</v>
+        <v>560</v>
       </c>
       <c r="G131" t="n">
-        <v>112.09</v>
+        <v>364.55</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L131" t="n">
+        <v>104</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:18.936</t>
+          <t>2026-05-29 09:36:24.490</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421761100</v>
+        <v>1780022183239</v>
       </c>
       <c r="C132" t="n">
-        <v>87979</v>
+        <v>88085</v>
       </c>
       <c r="D132" t="n">
-        <v>-423.17</v>
+        <v>124.87</v>
       </c>
       <c r="E132" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F132" t="n">
-        <v>886</v>
+        <v>560</v>
       </c>
       <c r="G132" t="n">
-        <v>112.09</v>
+        <v>364.55</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L132" t="n">
+        <v>104</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.582</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:19.310</t>
+          <t>2026-05-29 09:36:24.838</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421761301</v>
+        <v>1780022183439</v>
       </c>
       <c r="C133" t="n">
-        <v>88198</v>
+        <v>88341</v>
       </c>
       <c r="D133" t="n">
-        <v>-183.01</v>
+        <v>374.63</v>
       </c>
       <c r="E133" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F133" t="n">
-        <v>886</v>
+        <v>560</v>
       </c>
       <c r="G133" t="n">
-        <v>112.09</v>
+        <v>364.55</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1398</v>
+      </c>
+      <c r="L133" t="n">
+        <v>103</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.757</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:19.312</t>
+          <t>2026-05-29 09:36:24.862</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779421761503</v>
+        <v>1780022183639</v>
       </c>
       <c r="C134" t="n">
-        <v>87998</v>
+        <v>88413</v>
       </c>
       <c r="D134" t="n">
-        <v>-373.86</v>
+        <v>427.9</v>
       </c>
       <c r="E134" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F134" t="n">
-        <v>786</v>
+        <v>520</v>
       </c>
       <c r="G134" t="n">
-        <v>112.09</v>
+        <v>375.03</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J134" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L134" t="n">
+        <v>109</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.963</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:19.742</t>
+          <t>2026-05-29 09:36:24.885</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779421761704</v>
+        <v>1780022183839</v>
       </c>
       <c r="C135" t="n">
-        <v>87916</v>
+        <v>88653</v>
       </c>
       <c r="D135" t="n">
-        <v>-437.17</v>
+        <v>646.5</v>
       </c>
       <c r="E135" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F135" t="n">
-        <v>786</v>
+        <v>520</v>
       </c>
       <c r="G135" t="n">
-        <v>112.09</v>
+        <v>375.03</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J135" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L135" t="n">
+        <v>108</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.377</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:19.743</t>
+          <t>2026-05-29 09:36:25.565</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779421761906</v>
+        <v>1780022184058</v>
       </c>
       <c r="C136" t="n">
-        <v>88070</v>
+        <v>87903</v>
       </c>
       <c r="D136" t="n">
-        <v>-261.31</v>
+        <v>-135.82</v>
       </c>
       <c r="E136" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F136" t="n">
-        <v>786</v>
+        <v>520</v>
       </c>
       <c r="G136" t="n">
-        <v>112.09</v>
+        <v>375.03</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1506</v>
+      </c>
+      <c r="L136" t="n">
+        <v>108</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.292</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:20.123</t>
+          <t>2026-05-29 09:36:25.567</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779421762107</v>
+        <v>1780022184258</v>
       </c>
       <c r="C137" t="n">
-        <v>88404</v>
+        <v>88421</v>
       </c>
       <c r="D137" t="n">
-        <v>85.76000000000001</v>
+        <v>388.97</v>
       </c>
       <c r="E137" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F137" t="n">
-        <v>704</v>
+        <v>520</v>
       </c>
       <c r="G137" t="n">
-        <v>117.67</v>
+        <v>375.03</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1308</v>
+      </c>
+      <c r="L137" t="n">
+        <v>105</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:20.125</t>
+          <t>2026-05-29 09:36:25.568</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779421762308</v>
+        <v>1780022184458</v>
       </c>
       <c r="C138" t="n">
-        <v>88144</v>
+        <v>88522</v>
       </c>
       <c r="D138" t="n">
-        <v>-178.53</v>
+        <v>470.52</v>
       </c>
       <c r="E138" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F138" t="n">
-        <v>704</v>
+        <v>859</v>
       </c>
       <c r="G138" t="n">
-        <v>117.67</v>
+        <v>349.62</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1109</v>
+      </c>
+      <c r="L138" t="n">
+        <v>105</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.244</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:49:20.549</t>
+          <t>2026-05-29 09:36:27.460</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779421762510</v>
+        <v>1780022184658</v>
       </c>
       <c r="C139" t="n">
-        <v>87937</v>
+        <v>88418</v>
       </c>
       <c r="D139" t="n">
-        <v>-376.61</v>
+        <v>342.99</v>
       </c>
       <c r="E139" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F139" t="n">
-        <v>704</v>
+        <v>859</v>
       </c>
       <c r="G139" t="n">
-        <v>117.67</v>
+        <v>349.62</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:20.550</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779421762711</v>
-      </c>
-      <c r="C140" t="n">
-        <v>88052</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-242.78</v>
-      </c>
-      <c r="E140" t="n">
-        <v>75</v>
-      </c>
-      <c r="F140" t="n">
-        <v>704</v>
-      </c>
-      <c r="G140" t="n">
-        <v>117.67</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:20.971</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779421762913</v>
-      </c>
-      <c r="C141" t="n">
-        <v>88305</v>
-      </c>
-      <c r="D141" t="n">
-        <v>22.36</v>
-      </c>
-      <c r="E141" t="n">
-        <v>75</v>
-      </c>
-      <c r="F141" t="n">
-        <v>704</v>
-      </c>
-      <c r="G141" t="n">
-        <v>117.67</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:20.975</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779421763114</v>
-      </c>
-      <c r="C142" t="n">
-        <v>88086</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-197.75</v>
-      </c>
-      <c r="E142" t="n">
-        <v>73</v>
-      </c>
-      <c r="F142" t="n">
-        <v>907</v>
-      </c>
-      <c r="G142" t="n">
-        <v>115.87</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:21.362</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779421763315</v>
-      </c>
-      <c r="C143" t="n">
-        <v>87880</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-393.87</v>
-      </c>
-      <c r="E143" t="n">
-        <v>73</v>
-      </c>
-      <c r="F143" t="n">
-        <v>907</v>
-      </c>
-      <c r="G143" t="n">
-        <v>115.87</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:21.364</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779421763517</v>
-      </c>
-      <c r="C144" t="n">
-        <v>88053</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-201.17</v>
-      </c>
-      <c r="E144" t="n">
-        <v>73</v>
-      </c>
-      <c r="F144" t="n">
-        <v>907</v>
-      </c>
-      <c r="G144" t="n">
-        <v>115.87</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:21.805</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779421763718</v>
-      </c>
-      <c r="C145" t="n">
-        <v>88378</v>
-      </c>
-      <c r="D145" t="n">
-        <v>133.88</v>
-      </c>
-      <c r="E145" t="n">
-        <v>76</v>
-      </c>
-      <c r="F145" t="n">
-        <v>765</v>
-      </c>
-      <c r="G145" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:21.806</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779421763920</v>
-      </c>
-      <c r="C146" t="n">
-        <v>88005</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-245.81</v>
-      </c>
-      <c r="E146" t="n">
-        <v>76</v>
-      </c>
-      <c r="F146" t="n">
-        <v>765</v>
-      </c>
-      <c r="G146" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:22.172</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779421764121</v>
-      </c>
-      <c r="C147" t="n">
-        <v>87991</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-247.52</v>
-      </c>
-      <c r="E147" t="n">
-        <v>76</v>
-      </c>
-      <c r="F147" t="n">
-        <v>765</v>
-      </c>
-      <c r="G147" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:22.174</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779421764322</v>
-      </c>
-      <c r="C148" t="n">
-        <v>88101</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-125.14</v>
-      </c>
-      <c r="E148" t="n">
-        <v>76</v>
-      </c>
-      <c r="F148" t="n">
-        <v>765</v>
-      </c>
-      <c r="G148" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:22.616</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421764524</v>
-      </c>
-      <c r="C149" t="n">
-        <v>88271</v>
-      </c>
-      <c r="D149" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="E149" t="n">
-        <v>76</v>
-      </c>
-      <c r="F149" t="n">
-        <v>785</v>
-      </c>
-      <c r="G149" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:22.617</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421764725</v>
-      </c>
-      <c r="C150" t="n">
-        <v>87721</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-501.44</v>
-      </c>
-      <c r="E150" t="n">
-        <v>76</v>
-      </c>
-      <c r="F150" t="n">
-        <v>785</v>
-      </c>
-      <c r="G150" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:23.111</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421764927</v>
-      </c>
-      <c r="C151" t="n">
-        <v>87944</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-253.37</v>
-      </c>
-      <c r="E151" t="n">
-        <v>76</v>
-      </c>
-      <c r="F151" t="n">
-        <v>785</v>
-      </c>
-      <c r="G151" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:23.112</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779421765128</v>
-      </c>
-      <c r="C152" t="n">
-        <v>88100</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-84.7</v>
-      </c>
-      <c r="E152" t="n">
-        <v>76</v>
-      </c>
-      <c r="F152" t="n">
-        <v>785</v>
-      </c>
-      <c r="G152" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:23.398</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779421765329</v>
-      </c>
-      <c r="C153" t="n">
-        <v>88298</v>
-      </c>
-      <c r="D153" t="n">
-        <v>117.53</v>
-      </c>
-      <c r="E153" t="n">
-        <v>75</v>
-      </c>
-      <c r="F153" t="n">
-        <v>726</v>
-      </c>
-      <c r="G153" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:23.399</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1779421765531</v>
-      </c>
-      <c r="C154" t="n">
-        <v>87710</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-476.34</v>
-      </c>
-      <c r="E154" t="n">
-        <v>75</v>
-      </c>
-      <c r="F154" t="n">
-        <v>726</v>
-      </c>
-      <c r="G154" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:49:23.829</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1779421765732</v>
-      </c>
-      <c r="C155" t="n">
-        <v>87838</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-324.53</v>
-      </c>
-      <c r="E155" t="n">
-        <v>75</v>
-      </c>
-      <c r="F155" t="n">
-        <v>726</v>
-      </c>
-      <c r="G155" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I139" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2801</v>
+      </c>
+      <c r="L139" t="n">
+        <v>108</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.948</v>
       </c>
     </row>
   </sheetData>
